--- a/it_forms/007_it_services_fee_schedule_request--it_forms.xlsx
+++ b/it_forms/007_it_services_fee_schedule_request--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -528,10 +528,14 @@
           <t>Service Options</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Briefly describe your services and pricing.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -551,17 +555,21 @@
           <t>Contact Information</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter your name, phone number, and email.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -574,10 +582,14 @@
           <t>Service Times</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Available service hours.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -597,53 +609,65 @@
           <t>Pricing</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select your pricing option.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>service_times_2</t>
+          <t>service_details</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Service Times</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Service Details</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Provide more details about your services.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pricing_2</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pricing</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Any other information you would like to share.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,23 +677,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>service_options_2</t>
+          <t>payment_terms</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Service Options</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Payment Terms</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select payment terms.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Contact Information</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Leave a review about our services.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -710,9 +742,9 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,153 +767,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pricing_choices</t>
+          <t>service_times_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>monday,_9:00_am_-_5:00_pm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Monday, 9:00 AM - 5:00 PM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pricing_choices</t>
+          <t>service_times_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>tuesday,_9:00_am_-_5:00_pm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Tuesday, 9:00 AM - 5:00 PM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pricing_choices</t>
+          <t>service_times_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>wednesday,_9:00_am_-_5:00_pm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Wednesday, 9:00 AM - 5:00 PM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>service_times_2_choices</t>
+          <t>pricing_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>service_times_2_choices</t>
+          <t>pricing_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>service_times_2_choices</t>
+          <t>pricing_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pricing_2_choices</t>
+          <t>payment_terms_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pricing_2_choices</t>
+          <t>payment_terms_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pricing_2_choices</t>
+          <t>payment_terms_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
